--- a/research/traditional_assets/database/data/south_africa/south_africa_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_telecom_equipment.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,28 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0415</v>
-      </c>
-      <c r="E2">
-        <v>0.178</v>
+        <v>-0.0626</v>
       </c>
       <c r="G2">
-        <v>-0.08033222591362127</v>
+        <v>-0.06408839779005525</v>
       </c>
       <c r="H2">
-        <v>-0.08421926910299003</v>
+        <v>-0.06408839779005525</v>
       </c>
       <c r="I2">
-        <v>-0.08239202657807308</v>
+        <v>-0.06703499079189687</v>
       </c>
       <c r="J2">
-        <v>-0.08239202657807308</v>
+        <v>-0.06703499079189687</v>
       </c>
       <c r="K2">
-        <v>7.32</v>
+        <v>-4.65</v>
       </c>
       <c r="L2">
-        <v>0.1215946843853821</v>
+        <v>-0.08563535911602212</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.183999999999999</v>
+        <v>0.197</v>
       </c>
       <c r="V2">
-        <v>0.2040141676505313</v>
+        <v>0.06480263157894738</v>
       </c>
       <c r="W2">
-        <v>0.05991678224687932</v>
+        <v>-0.5502958579881657</v>
       </c>
       <c r="X2">
-        <v>0.2451450558689477</v>
+        <v>0.4028168892364662</v>
       </c>
       <c r="Y2">
-        <v>-0.1852282736220684</v>
+        <v>-0.9531127472246319</v>
       </c>
       <c r="Z2">
-        <v>1.429283696194117</v>
+        <v>2.772246898453055</v>
       </c>
       <c r="AA2">
-        <v>-0.1182555956321953</v>
+        <v>-0.1858375453106652</v>
       </c>
       <c r="AB2">
-        <v>0.1677750450172027</v>
+        <v>0.14102558384408</v>
       </c>
       <c r="AC2">
-        <v>-0.2860306406493979</v>
+        <v>-0.3268631291547452</v>
       </c>
       <c r="AD2">
-        <v>13.35</v>
+        <v>10.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>13.35</v>
+        <v>10.2</v>
       </c>
       <c r="AG2">
-        <v>8.166</v>
+        <v>10.003</v>
       </c>
       <c r="AH2">
-        <v>0.3444272445820434</v>
+        <v>0.770392749244713</v>
       </c>
       <c r="AI2">
-        <v>0.3237148399612027</v>
+        <v>0.7956318252730108</v>
       </c>
       <c r="AJ2">
-        <v>0.2432094353109364</v>
+        <v>0.7669247872421989</v>
       </c>
       <c r="AK2">
-        <v>0.2264810295096517</v>
+        <v>0.7924423671076606</v>
       </c>
       <c r="AL2">
-        <v>1.374</v>
+        <v>1.16</v>
       </c>
       <c r="AM2">
-        <v>1.263</v>
+        <v>1.113</v>
       </c>
       <c r="AN2">
-        <v>-3.178571428571428</v>
+        <v>-2.931034482758621</v>
       </c>
       <c r="AO2">
-        <v>-3.609898107714701</v>
+        <v>-3.137931034482759</v>
       </c>
       <c r="AP2">
-        <v>-1.944285714285714</v>
+        <v>-2.874425287356322</v>
       </c>
       <c r="AQ2">
-        <v>-3.927157561361836</v>
+        <v>-3.270440251572327</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Etion Limited (JSE:ETO)</t>
+          <t>Ellies Holdings Limited (JSE:ELI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,11 +715,26 @@
           <t>Telecom. Equipment</t>
         </is>
       </c>
-      <c r="E3">
-        <v>0.178</v>
+      <c r="D3">
+        <v>-0.0626</v>
+      </c>
+      <c r="G3">
+        <v>-0.06408839779005525</v>
+      </c>
+      <c r="H3">
+        <v>-0.06408839779005525</v>
+      </c>
+      <c r="I3">
+        <v>-0.06703499079189687</v>
+      </c>
+      <c r="J3">
+        <v>-0.06703499079189687</v>
       </c>
       <c r="K3">
-        <v>10.5</v>
+        <v>-4.65</v>
+      </c>
+      <c r="L3">
+        <v>-0.08563535911602212</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -731,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -740,207 +752,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.56</v>
+        <v>0.197</v>
       </c>
       <c r="V3">
-        <v>0.2491803278688524</v>
+        <v>0.06480263157894738</v>
       </c>
       <c r="W3">
-        <v>0.4285714285714285</v>
+        <v>-0.5502958579881657</v>
       </c>
       <c r="X3">
-        <v>0.187486779662943</v>
+        <v>0.4028168892364662</v>
       </c>
       <c r="Y3">
-        <v>0.2410846489084855</v>
+        <v>-0.9531127472246319</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.772246898453055</v>
       </c>
       <c r="AA3">
-        <v>-0.1055758683729433</v>
+        <v>-0.1858375453106652</v>
       </c>
       <c r="AB3">
-        <v>0.16847228910848</v>
+        <v>0.14102558384408</v>
       </c>
       <c r="AC3">
-        <v>-0.2740481574814233</v>
+        <v>-0.3268631291547452</v>
       </c>
       <c r="AD3">
-        <v>3.43</v>
+        <v>10.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.43</v>
+        <v>10.2</v>
       </c>
       <c r="AG3">
-        <v>-1.129999999999999</v>
+        <v>10.003</v>
       </c>
       <c r="AH3">
-        <v>0.1578462954440865</v>
+        <v>0.770392749244713</v>
       </c>
       <c r="AI3">
-        <v>0.1322792132664867</v>
+        <v>0.7956318252730108</v>
       </c>
       <c r="AJ3">
-        <v>-0.06581246359930107</v>
+        <v>0.7669247872421989</v>
       </c>
       <c r="AK3">
-        <v>-0.05287786616752454</v>
+        <v>0.7924423671076606</v>
       </c>
       <c r="AL3">
-        <v>0.46</v>
+        <v>1.16</v>
       </c>
       <c r="AM3">
-        <v>0.349</v>
+        <v>1.113</v>
       </c>
       <c r="AN3">
-        <v>-1.96</v>
+        <v>-2.931034482758621</v>
       </c>
       <c r="AO3">
-        <v>-5.021739130434782</v>
+        <v>-3.137931034482759</v>
       </c>
       <c r="AP3">
-        <v>0.6457142857142854</v>
+        <v>-2.874425287356322</v>
       </c>
       <c r="AQ3">
-        <v>-6.6189111747851</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ellies Holdings Limited (JSE:ELI)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Telecom. Equipment</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-0.0415</v>
-      </c>
-      <c r="G4">
-        <v>-0.05514950166112956</v>
-      </c>
-      <c r="H4">
-        <v>-0.05514950166112956</v>
-      </c>
-      <c r="I4">
-        <v>-0.04401993355481727</v>
-      </c>
-      <c r="J4">
-        <v>-0.04401993355481727</v>
-      </c>
-      <c r="K4">
-        <v>-3.18</v>
-      </c>
-      <c r="L4">
-        <v>-0.05282392026578073</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0.624</v>
-      </c>
-      <c r="V4">
-        <v>0.08776371308016877</v>
-      </c>
-      <c r="W4">
-        <v>-0.3087378640776699</v>
-      </c>
-      <c r="X4">
-        <v>0.3028033320749525</v>
-      </c>
-      <c r="Y4">
-        <v>-0.6115411961526224</v>
-      </c>
-      <c r="Z4">
-        <v>2.974455259647216</v>
-      </c>
-      <c r="AA4">
-        <v>-0.1309353228914472</v>
-      </c>
-      <c r="AB4">
-        <v>0.1670778009259253</v>
-      </c>
-      <c r="AC4">
-        <v>-0.2980131238173725</v>
-      </c>
-      <c r="AD4">
-        <v>9.92</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>9.92</v>
-      </c>
-      <c r="AG4">
-        <v>9.295999999999999</v>
-      </c>
-      <c r="AH4">
-        <v>0.5825014679976511</v>
-      </c>
-      <c r="AI4">
-        <v>0.6479425212279556</v>
-      </c>
-      <c r="AJ4">
-        <v>0.5666219675728392</v>
-      </c>
-      <c r="AK4">
-        <v>0.6329837940896091</v>
-      </c>
-      <c r="AL4">
-        <v>0.914</v>
-      </c>
-      <c r="AM4">
-        <v>0.914</v>
-      </c>
-      <c r="AN4">
-        <v>-4.048979591836734</v>
-      </c>
-      <c r="AO4">
-        <v>-2.899343544857768</v>
-      </c>
-      <c r="AP4">
-        <v>-3.794285714285714</v>
-      </c>
-      <c r="AQ4">
-        <v>-2.899343544857768</v>
+        <v>-3.270440251572327</v>
       </c>
     </row>
   </sheetData>
